--- a/data/source/weekly/cs-en-us-009pct.xlsx
+++ b/data/source/weekly/cs-en-us-009pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -911,7 +911,7 @@
         <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>20</v>
@@ -920,13 +920,13 @@
         <v>21</v>
       </c>
       <c r="L15" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="M15" s="14">
+        <v>200</v>
       </c>
       <c r="N15" s="14">
-        <v>-60</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
         <v>5</v>
       </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
         <v>7</v>
       </c>
       <c r="J16" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K16" s="14">
+        <v>-46.153846153846</v>
+      </c>
+      <c r="L16" s="14">
+        <v>-61.111111111111</v>
+      </c>
+      <c r="M16" s="14">
         <v>-41.666666666666</v>
       </c>
-      <c r="L16" s="14">
-        <v>-56.25</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-36.363636363636</v>
-      </c>
       <c r="N16" s="14">
-        <v>-92.222222222222</v>
+        <v>-93.457943925233</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
         <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G17" s="15">
         <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>-26.315789473684</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="I17" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J17" s="15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K17" s="14">
-        <v>-5</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L17" s="14">
-        <v>-32.142857142857</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="M17" s="14">
-        <v>58.333333333333</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>-71.641791044776</v>
+        <v>-69.014084507042</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
         <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18" s="15">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H18" s="14">
-        <v>-35.294117647058</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I18" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K18" s="14">
-        <v>-38.095238095238</v>
+        <v>-44</v>
       </c>
       <c r="L18" s="14">
-        <v>-38.095238095238</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M18" s="14">
-        <v>-63.888888888888</v>
+        <v>-69.565217391304</v>
       </c>
       <c r="N18" s="14">
-        <v>-88.695652173913</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D19" s="15">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>-52.631578947368</v>
+        <v>20</v>
       </c>
       <c r="F19" s="15">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G19" s="15">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H19" s="14">
-        <v>-32.142857142857</v>
+        <v>-18.867924528301</v>
       </c>
       <c r="I19" s="15">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="J19" s="15">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K19" s="14">
-        <v>-20.779220779220</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="L19" s="14">
-        <v>-30.681818181818</v>
+        <v>-25</v>
       </c>
       <c r="M19" s="14">
-        <v>-28.235294117647</v>
+        <v>-32.075471698113</v>
       </c>
       <c r="N19" s="14">
-        <v>-61.875</v>
+        <v>-60.439560439560</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>-83.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="15">
         <v>6</v>
       </c>
       <c r="K20" s="14">
-        <v>-83.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L20" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M20" s="14">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.959183673469</v>
+        <v>-96.666666666666</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H21" s="18">
-        <v>-32.692307692307</v>
+        <v>-20.430107526881</v>
       </c>
       <c r="I21" s="17">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="J21" s="17">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="K21" s="18">
-        <v>-24.264705882352</v>
+        <v>-22.077922077922</v>
       </c>
       <c r="L21" s="18">
-        <v>-34.810126582278</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="M21" s="18">
-        <v>-30.405405405405</v>
+        <v>-34.065934065934</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.893442622950</v>
+        <v>-78.339350180505</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>3</v>
-      </c>
-      <c r="D23" s="15">
-        <v>2</v>
-      </c>
-      <c r="E23" s="14">
-        <v>50</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
         <v>11</v>
       </c>
       <c r="G23" s="15">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H23" s="14">
-        <v>-21.428571428571</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I23" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J23" s="15">
         <v>16</v>
       </c>
       <c r="K23" s="14">
-        <v>-6.25</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M23" s="14">
-        <v>7.142857142857</v>
+        <v>6.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D24" s="15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E24" s="14">
-        <v>21.739130434782</v>
+        <v>45.454545454545</v>
       </c>
       <c r="F24" s="15">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G24" s="15">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H24" s="14">
-        <v>-1.785714285714</v>
+        <v>1.923076923076</v>
       </c>
       <c r="I24" s="15">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="J24" s="15">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="K24" s="14">
-        <v>3.921568627450</v>
+        <v>8.571428571428</v>
       </c>
       <c r="L24" s="14">
-        <v>25.196850393700</v>
+        <v>25.827814569536</v>
       </c>
       <c r="M24" s="14">
-        <v>1.923076923076</v>
+        <v>4.972375690607</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D25" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E25" s="14">
-        <v>27.272727272727</v>
+        <v>110</v>
       </c>
       <c r="F25" s="15">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G25" s="15">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H25" s="14">
-        <v>13.725490196078</v>
+        <v>22.916666666666</v>
       </c>
       <c r="I25" s="15">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="J25" s="15">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K25" s="14">
-        <v>28.358208955223</v>
+        <v>38.961038961039</v>
       </c>
       <c r="L25" s="14">
-        <v>24.637681159420</v>
+        <v>37.179487179487</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>-14.285714285714</v>
+        <v>150</v>
       </c>
       <c r="F26" s="15">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G26" s="15">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H26" s="14">
-        <v>22.727272727272</v>
+        <v>72.222222222222</v>
       </c>
       <c r="I26" s="15">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="J26" s="15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K26" s="14">
-        <v>7.894736842105</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L26" s="14">
-        <v>-4.651162790697</v>
+        <v>4.081632653061</v>
       </c>
       <c r="M26" s="14">
-        <v>-2.380952380952</v>
+        <v>-7.272727272727</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1403,7 +1403,7 @@
         <v>21</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>21</v>
       </c>
       <c r="L27" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>-71.428571428571</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="15">
         <v>3</v>
       </c>
       <c r="J28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="14">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="L28" s="14">
         <v>-50</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="15">
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="15">
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-009pct.xlsx
+++ b/data/source/weekly/cs-en-us-009pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -926,7 +926,7 @@
         <v>200</v>
       </c>
       <c r="N15" s="14">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -943,31 +943,31 @@
         <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="14">
         <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J16" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="14">
-        <v>-46.153846153846</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L16" s="14">
-        <v>-61.111111111111</v>
+        <v>-65.217391304347</v>
       </c>
       <c r="M16" s="14">
-        <v>-41.666666666666</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="N16" s="14">
-        <v>-93.457943925233</v>
+        <v>-93.388429752066</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>5</v>
+      </c>
+      <c r="D17" s="15">
         <v>2</v>
       </c>
-      <c r="D17" s="15">
-        <v>3</v>
-      </c>
       <c r="E17" s="14">
-        <v>-33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="F17" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17" s="15">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H17" s="14">
-        <v>-36.842105263157</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I17" s="15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J17" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K17" s="14">
-        <v>-4.347826086956</v>
+        <v>8</v>
       </c>
       <c r="L17" s="14">
-        <v>-24.137931034482</v>
+        <v>-10</v>
       </c>
       <c r="M17" s="14">
-        <v>83.333333333333</v>
+        <v>58.823529411764</v>
       </c>
       <c r="N17" s="14">
-        <v>-69.014084507042</v>
+        <v>-64.935064935064</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
         <v>14</v>
       </c>
       <c r="H18" s="14">
-        <v>-28.571428571428</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K18" s="14">
-        <v>-44</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L18" s="14">
-        <v>-36.363636363636</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M18" s="14">
-        <v>-69.565217391304</v>
+        <v>-69.387755102040</v>
       </c>
       <c r="N18" s="14">
-        <v>-88.888888888888</v>
+        <v>-89.361702127659</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,54 +1057,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19" s="15">
         <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F19" s="15">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G19" s="15">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H19" s="14">
-        <v>-18.867924528301</v>
+        <v>-6.122448979591</v>
       </c>
       <c r="I19" s="15">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="J19" s="15">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="K19" s="14">
-        <v>-17.241379310344</v>
+        <v>-10.309278350515</v>
       </c>
       <c r="L19" s="14">
-        <v>-25</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="M19" s="14">
-        <v>-32.075471698113</v>
+        <v>-28.099173553719</v>
       </c>
       <c r="N19" s="14">
-        <v>-60.439560439560</v>
+        <v>-58.173076923076</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="15">
+        <v>2</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
         <v>2</v>
@@ -1119,19 +1119,19 @@
         <v>2</v>
       </c>
       <c r="J20" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K20" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L20" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M20" s="14">
         <v>-60</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.666666666666</v>
+        <v>-97.183098591549</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>29.411764705882</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.430107526881</v>
+        <v>-6.25</v>
       </c>
       <c r="I21" s="17">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="J21" s="17">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="K21" s="18">
-        <v>-22.077922077922</v>
+        <v>-16.959064327485</v>
       </c>
       <c r="L21" s="18">
-        <v>-29.411764705882</v>
+        <v>-27.918781725888</v>
       </c>
       <c r="M21" s="18">
-        <v>-34.065934065934</v>
+        <v>-31.730769230769</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.339350180505</v>
+        <v>-77.352472089314</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G23" s="15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H23" s="14">
-        <v>57.142857142857</v>
+        <v>300</v>
       </c>
       <c r="I23" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J23" s="15">
         <v>16</v>
       </c>
       <c r="K23" s="14">
+        <v>6.25</v>
+      </c>
+      <c r="L23" s="14">
+        <v>88.888888888888</v>
+      </c>
+      <c r="M23" s="14">
         <v>0</v>
-      </c>
-      <c r="L23" s="14">
-        <v>100</v>
-      </c>
-      <c r="M23" s="14">
-        <v>6.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D24" s="15">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E24" s="14">
-        <v>45.454545454545</v>
+        <v>3.571428571428</v>
       </c>
       <c r="F24" s="15">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G24" s="15">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H24" s="14">
-        <v>1.923076923076</v>
+        <v>4.761904761904</v>
       </c>
       <c r="I24" s="15">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="J24" s="15">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="K24" s="14">
-        <v>8.571428571428</v>
+        <v>7.389162561576</v>
       </c>
       <c r="L24" s="14">
-        <v>25.827814569536</v>
+        <v>20.441988950276</v>
       </c>
       <c r="M24" s="14">
-        <v>4.972375690607</v>
+        <v>3.317535545023</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D25" s="15">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E25" s="14">
-        <v>110</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F25" s="15">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G25" s="15">
         <v>48</v>
       </c>
       <c r="H25" s="14">
-        <v>22.916666666666</v>
+        <v>31.25</v>
       </c>
       <c r="I25" s="15">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="J25" s="15">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="K25" s="14">
-        <v>38.961038961039</v>
+        <v>29.787234042553</v>
       </c>
       <c r="L25" s="14">
-        <v>37.179487179487</v>
+        <v>38.636363636363</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G26" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H26" s="14">
-        <v>72.222222222222</v>
+        <v>70</v>
       </c>
       <c r="I26" s="15">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="J26" s="15">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K26" s="14">
-        <v>21.428571428571</v>
+        <v>25</v>
       </c>
       <c r="L26" s="14">
-        <v>4.081632653061</v>
+        <v>13.207547169811</v>
       </c>
       <c r="M26" s="14">
-        <v>-7.272727272727</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1438,22 +1438,22 @@
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="15">
         <v>3</v>
       </c>
       <c r="J28" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="14">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="L28" s="14">
         <v>-62.5</v>
-      </c>
-      <c r="L28" s="14">
-        <v>-50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-009pct.xlsx
+++ b/data/source/weekly/cs-en-us-009pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>-100</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
@@ -884,7 +884,7 @@
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -901,8 +901,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="15">
-        <v>2</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -910,7 +910,7 @@
       <c r="H15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="14">
         <v>3</v>
       </c>
       <c r="J15" s="13" t="s">
@@ -919,13 +919,13 @@
       <c r="K15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="15">
         <v>0</v>
       </c>
-      <c r="M15" s="14">
+      <c r="M15" s="15">
         <v>200</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="15">
         <v>-57.142857142857</v>
       </c>
     </row>
@@ -933,205 +933,205 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>0</v>
-      </c>
-      <c r="F16" s="15">
-        <v>4</v>
-      </c>
-      <c r="G16" s="15">
-        <v>4</v>
-      </c>
-      <c r="H16" s="14">
-        <v>0</v>
-      </c>
-      <c r="I16" s="15">
-        <v>8</v>
-      </c>
-      <c r="J16" s="15">
-        <v>14</v>
-      </c>
-      <c r="K16" s="14">
-        <v>-42.857142857142</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-65.217391304347</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-46.666666666666</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-93.388429752066</v>
+      <c r="D16" s="14">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F16" s="14">
+        <v>5</v>
+      </c>
+      <c r="G16" s="14">
+        <v>7</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-28.571428571428</v>
+      </c>
+      <c r="I16" s="14">
+        <v>10</v>
+      </c>
+      <c r="J16" s="14">
+        <v>17</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-41.176470588235</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-58.333333333333</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-47.368421052631</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-92.481203007518</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>5</v>
-      </c>
-      <c r="D17" s="15">
+      <c r="C17" s="14">
         <v>2</v>
       </c>
-      <c r="E17" s="14">
-        <v>150</v>
-      </c>
-      <c r="F17" s="15">
+      <c r="D17" s="14">
+        <v>8</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-75</v>
+      </c>
+      <c r="F17" s="14">
         <v>13</v>
       </c>
-      <c r="G17" s="15">
-        <v>11</v>
-      </c>
-      <c r="H17" s="14">
-        <v>18.181818181818</v>
-      </c>
-      <c r="I17" s="15">
-        <v>27</v>
-      </c>
-      <c r="J17" s="15">
-        <v>25</v>
-      </c>
-      <c r="K17" s="14">
-        <v>8</v>
-      </c>
-      <c r="L17" s="14">
-        <v>-10</v>
-      </c>
-      <c r="M17" s="14">
-        <v>58.823529411764</v>
-      </c>
-      <c r="N17" s="14">
-        <v>-64.935064935064</v>
+      <c r="G17" s="14">
+        <v>16</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-18.75</v>
+      </c>
+      <c r="I17" s="14">
+        <v>30</v>
+      </c>
+      <c r="J17" s="14">
+        <v>33</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-9.090909090909</v>
+      </c>
+      <c r="L17" s="15">
+        <v>-6.25</v>
+      </c>
+      <c r="M17" s="15">
+        <v>57.894736842105</v>
+      </c>
+      <c r="N17" s="15">
+        <v>-66.292134831460</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15">
-        <v>2</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F18" s="15">
-        <v>8</v>
-      </c>
-      <c r="G18" s="15">
-        <v>14</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-42.857142857142</v>
-      </c>
-      <c r="I18" s="15">
-        <v>15</v>
-      </c>
-      <c r="J18" s="15">
-        <v>27</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-44.444444444444</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-44.444444444444</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-69.387755102040</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-89.361702127659</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="14">
+        <v>7</v>
+      </c>
+      <c r="G18" s="14">
+        <v>13</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-46.153846153846</v>
+      </c>
+      <c r="I18" s="14">
+        <v>16</v>
+      </c>
+      <c r="J18" s="14">
+        <v>30</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-46.666666666666</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-44.827586206896</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-70.909090909090</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-89.677419354838</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="14">
+        <v>12</v>
+      </c>
+      <c r="D19" s="14">
         <v>15</v>
       </c>
-      <c r="D19" s="15">
-        <v>10</v>
-      </c>
-      <c r="E19" s="14">
-        <v>50</v>
-      </c>
-      <c r="F19" s="15">
-        <v>46</v>
-      </c>
-      <c r="G19" s="15">
-        <v>49</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-6.122448979591</v>
-      </c>
-      <c r="I19" s="15">
-        <v>87</v>
-      </c>
-      <c r="J19" s="15">
-        <v>97</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-10.309278350515</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-21.621621621621</v>
-      </c>
-      <c r="M19" s="14">
-        <v>-28.099173553719</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-58.173076923076</v>
+      <c r="E19" s="15">
+        <v>-20</v>
+      </c>
+      <c r="F19" s="14">
+        <v>47</v>
+      </c>
+      <c r="G19" s="14">
+        <v>54</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-12.962962962963</v>
+      </c>
+      <c r="I19" s="14">
+        <v>100</v>
+      </c>
+      <c r="J19" s="14">
+        <v>112</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-10.714285714285</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-18.032786885245</v>
+      </c>
+      <c r="M19" s="15">
+        <v>-22.480620155038</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-56.709956709956</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
+        <v>3</v>
+      </c>
+      <c r="G20" s="14">
         <v>2</v>
       </c>
-      <c r="E20" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="15">
-        <v>2</v>
-      </c>
-      <c r="G20" s="15">
-        <v>2</v>
-      </c>
-      <c r="H20" s="14">
+      <c r="H20" s="15">
+        <v>50</v>
+      </c>
+      <c r="I20" s="14">
+        <v>3</v>
+      </c>
+      <c r="J20" s="14">
+        <v>8</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-62.5</v>
+      </c>
+      <c r="L20" s="15">
         <v>0</v>
       </c>
-      <c r="I20" s="15">
-        <v>2</v>
-      </c>
-      <c r="J20" s="15">
-        <v>8</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-75</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="M20" s="14">
-        <v>-60</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-97.183098591549</v>
+      <c r="M20" s="15">
+        <v>-40</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-96.511627906976</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>29.411764705882</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G21" s="17">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.25</v>
+        <v>-18.279569892473</v>
       </c>
       <c r="I21" s="17">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="J21" s="17">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.959064327485</v>
+        <v>-19.402985074626</v>
       </c>
       <c r="L21" s="18">
-        <v>-27.918781725888</v>
+        <v>-23.943661971831</v>
       </c>
       <c r="M21" s="18">
-        <v>-31.730769230769</v>
+        <v>-28.947368421052</v>
       </c>
       <c r="N21" s="18">
-        <v>-77.352472089314</v>
+        <v>-76.988636363636</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,28 +1188,28 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>0</v>
-      </c>
-      <c r="I22" s="15">
-        <v>1</v>
-      </c>
-      <c r="J22" s="15">
+      <c r="J22" s="14">
         <v>3</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="15">
         <v>-75</v>
       </c>
-      <c r="M22" s="14">
+      <c r="M22" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="15">
-        <v>8</v>
-      </c>
-      <c r="G23" s="15">
+      <c r="C23" s="14">
         <v>2</v>
       </c>
-      <c r="H23" s="14">
-        <v>300</v>
-      </c>
-      <c r="I23" s="15">
-        <v>17</v>
-      </c>
-      <c r="J23" s="15">
-        <v>16</v>
-      </c>
-      <c r="K23" s="14">
-        <v>6.25</v>
-      </c>
-      <c r="L23" s="14">
-        <v>88.888888888888</v>
-      </c>
-      <c r="M23" s="14">
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
         <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>6</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="15">
+        <v>50</v>
+      </c>
+      <c r="I23" s="14">
+        <v>19</v>
+      </c>
+      <c r="J23" s="14">
+        <v>18</v>
+      </c>
+      <c r="K23" s="15">
+        <v>5.555555555555</v>
+      </c>
+      <c r="L23" s="15">
+        <v>111.111111111111</v>
+      </c>
+      <c r="M23" s="15">
+        <v>5.555555555555</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>29</v>
-      </c>
-      <c r="D24" s="15">
-        <v>28</v>
-      </c>
-      <c r="E24" s="14">
-        <v>3.571428571428</v>
-      </c>
-      <c r="F24" s="15">
-        <v>110</v>
-      </c>
-      <c r="G24" s="15">
-        <v>105</v>
-      </c>
-      <c r="H24" s="14">
-        <v>4.761904761904</v>
-      </c>
-      <c r="I24" s="15">
-        <v>218</v>
-      </c>
-      <c r="J24" s="15">
-        <v>203</v>
-      </c>
-      <c r="K24" s="14">
-        <v>7.389162561576</v>
-      </c>
-      <c r="L24" s="14">
-        <v>20.441988950276</v>
-      </c>
-      <c r="M24" s="14">
-        <v>3.317535545023</v>
+      <c r="C24" s="14">
+        <v>21</v>
+      </c>
+      <c r="D24" s="14">
+        <v>18</v>
+      </c>
+      <c r="E24" s="15">
+        <v>16.666666666666</v>
+      </c>
+      <c r="F24" s="14">
+        <v>106</v>
+      </c>
+      <c r="G24" s="14">
+        <v>91</v>
+      </c>
+      <c r="H24" s="15">
+        <v>16.483516483516</v>
+      </c>
+      <c r="I24" s="14">
+        <v>236</v>
+      </c>
+      <c r="J24" s="14">
+        <v>221</v>
+      </c>
+      <c r="K24" s="15">
+        <v>6.787330316742</v>
+      </c>
+      <c r="L24" s="15">
+        <v>15.121951219512</v>
+      </c>
+      <c r="M24" s="15">
+        <v>-2.880658436213</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>15</v>
-      </c>
-      <c r="D25" s="15">
-        <v>17</v>
-      </c>
-      <c r="E25" s="14">
-        <v>-11.764705882352</v>
-      </c>
-      <c r="F25" s="15">
-        <v>63</v>
-      </c>
-      <c r="G25" s="15">
-        <v>48</v>
-      </c>
-      <c r="H25" s="14">
-        <v>31.25</v>
-      </c>
-      <c r="I25" s="15">
-        <v>122</v>
-      </c>
-      <c r="J25" s="15">
-        <v>94</v>
-      </c>
-      <c r="K25" s="14">
-        <v>29.787234042553</v>
-      </c>
-      <c r="L25" s="14">
-        <v>38.636363636363</v>
+      <c r="C25" s="14">
+        <v>6</v>
+      </c>
+      <c r="D25" s="14">
+        <v>11</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-45.454545454545</v>
+      </c>
+      <c r="F25" s="14">
+        <v>56</v>
+      </c>
+      <c r="G25" s="14">
+        <v>49</v>
+      </c>
+      <c r="H25" s="15">
+        <v>14.285714285714</v>
+      </c>
+      <c r="I25" s="14">
+        <v>128</v>
+      </c>
+      <c r="J25" s="14">
+        <v>105</v>
+      </c>
+      <c r="K25" s="15">
+        <v>21.904761904761</v>
+      </c>
+      <c r="L25" s="15">
+        <v>24.271844660194</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="14">
+        <v>5</v>
+      </c>
+      <c r="D26" s="14">
         <v>9</v>
       </c>
-      <c r="D26" s="15">
-        <v>6</v>
-      </c>
-      <c r="E26" s="14">
-        <v>50</v>
-      </c>
-      <c r="F26" s="15">
-        <v>34</v>
-      </c>
-      <c r="G26" s="15">
-        <v>20</v>
-      </c>
-      <c r="H26" s="14">
-        <v>70</v>
-      </c>
-      <c r="I26" s="15">
-        <v>60</v>
-      </c>
-      <c r="J26" s="15">
-        <v>48</v>
-      </c>
-      <c r="K26" s="14">
-        <v>25</v>
-      </c>
-      <c r="L26" s="14">
-        <v>13.207547169811</v>
-      </c>
-      <c r="M26" s="14">
-        <v>-3.225806451612</v>
+      <c r="E26" s="15">
+        <v>-44.444444444444</v>
+      </c>
+      <c r="F26" s="14">
+        <v>30</v>
+      </c>
+      <c r="G26" s="14">
+        <v>26</v>
+      </c>
+      <c r="H26" s="15">
+        <v>15.384615384615</v>
+      </c>
+      <c r="I26" s="14">
+        <v>64</v>
+      </c>
+      <c r="J26" s="14">
+        <v>57</v>
+      </c>
+      <c r="K26" s="15">
+        <v>12.280701754386</v>
+      </c>
+      <c r="L26" s="15">
+        <v>10.344827586206</v>
+      </c>
+      <c r="M26" s="15">
+        <v>-11.111111111111</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,8 +1393,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="15">
-        <v>2</v>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1402,7 +1402,7 @@
       <c r="H27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="14">
         <v>3</v>
       </c>
       <c r="J27" s="13" t="s">
@@ -1411,7 +1411,7 @@
       <c r="K27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L27" s="14">
+      <c r="L27" s="15">
         <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
@@ -1428,32 +1428,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="15">
         <v>-100</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="14">
         <v>2</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I28" s="14">
         <v>3</v>
       </c>
-      <c r="H28" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="I28" s="15">
-        <v>3</v>
-      </c>
-      <c r="J28" s="15">
-        <v>9</v>
-      </c>
-      <c r="K28" s="14">
+      <c r="J28" s="14">
+        <v>10</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-70</v>
+      </c>
+      <c r="L28" s="15">
         <v>-66.666666666666</v>
-      </c>
-      <c r="L28" s="14">
-        <v>-62.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>-100</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1499,7 +1499,7 @@
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="14">
+      <c r="N29" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>-100</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1540,7 +1540,7 @@
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="14">
+      <c r="N30" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
-        <v>4</v>
+      <c r="F31" s="14">
+        <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,7 +1566,7 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="14">
         <v>4</v>
       </c>
       <c r="J31" s="13" t="s">
@@ -1634,7 +1634,7 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L33" s="15">
         <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>23</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>17</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>4</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>2</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>1</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>-50</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>-75</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-94.117647058823</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-95.652173913043</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>41</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>38</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>17</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>12</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>17</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>41.666666666666</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>0</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-55.263157894736</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>-58.536585365853</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>1135</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>1000</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>424</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>246</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>114</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-53.658536585365</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-73.113207547169</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-88.6</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-89.955947136563</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>539</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>580</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>272</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>198</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>183</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>-7.575757575757</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>-32.720588235294</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-68.448275862069</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-66.048237476808</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>1420</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>942</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>385</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>316</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>168</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-46.835443037974</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-56.363636363636</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-82.165605095541</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-88.169014084507</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>2054</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>1704</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>1239</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>738</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>818</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>10.840108401084</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>-33.979015334947</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-51.995305164319</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-60.175267770204</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>779</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>545</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>200</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>151</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>37</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-75.496688741721</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-81.5</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-93.211009174311</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-95.250320924261</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-009pct.xlsx
+++ b/data/source/weekly/cs-en-us-009pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -926,7 +926,7 @@
         <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
         <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="I16" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J16" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>-41.176470588235</v>
+        <v>-40</v>
       </c>
       <c r="L16" s="15">
-        <v>-58.333333333333</v>
+        <v>-52</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.368421052631</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.481203007518</v>
+        <v>-92.156862745098</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-75</v>
+        <v>20</v>
       </c>
       <c r="F17" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G17" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>-18.75</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I17" s="14">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J17" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K17" s="15">
-        <v>-9.090909090909</v>
+        <v>-2.631578947368</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.25</v>
+        <v>2.777777777777</v>
       </c>
       <c r="M17" s="15">
-        <v>57.894736842105</v>
+        <v>54.166666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>-66.292134831460</v>
+        <v>-61.052631578947</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-46.153846153846</v>
+        <v>-68.75</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K18" s="15">
-        <v>-46.666666666666</v>
+        <v>-51.351351351351</v>
       </c>
       <c r="L18" s="15">
-        <v>-44.827586206896</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M18" s="15">
-        <v>-70.909090909090</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.677419354838</v>
+        <v>-89.595375722543</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F19" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H19" s="15">
-        <v>-12.962962962963</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="I19" s="14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J19" s="14">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.714285714285</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.032786885245</v>
+        <v>-22.535211267605</v>
       </c>
       <c r="M19" s="15">
-        <v>-22.480620155038</v>
+        <v>-23.611111111111</v>
       </c>
       <c r="N19" s="15">
-        <v>-56.709956709956</v>
+        <v>-58.174904942965</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="15">
-        <v>-62.5</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-40</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.511627906976</v>
+        <v>-95.918367346938</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E21" s="18">
-        <v>-46.666666666666</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="F21" s="17">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G21" s="17">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.279569892473</v>
+        <v>-19.191919191919</v>
       </c>
       <c r="I21" s="17">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="J21" s="17">
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.402985074626</v>
+        <v>-21.702127659574</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.943661971831</v>
+        <v>-23.966942148760</v>
       </c>
       <c r="M21" s="18">
-        <v>-28.947368421052</v>
+        <v>-28.125</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.988636363636</v>
+        <v>-76.796973518285</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,29 +1182,29 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>1</v>
       </c>
       <c r="J22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L22" s="15">
         <v>-75</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>-12.5</v>
       </c>
       <c r="I23" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J23" s="14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K23" s="15">
-        <v>5.555555555555</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>111.111111111111</v>
+        <v>91.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>5.555555555555</v>
+        <v>9.523809523809</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E24" s="15">
-        <v>16.666666666666</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="F24" s="14">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G24" s="14">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H24" s="15">
-        <v>16.483516483516</v>
+        <v>4.123711340206</v>
       </c>
       <c r="I24" s="14">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="J24" s="14">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="K24" s="15">
-        <v>6.787330316742</v>
+        <v>3.2</v>
       </c>
       <c r="L24" s="15">
-        <v>15.121951219512</v>
+        <v>11.688311688311</v>
       </c>
       <c r="M24" s="15">
-        <v>-2.880658436213</v>
+        <v>-8.833922261484</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-45.454545454545</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="F25" s="14">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G25" s="14">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H25" s="15">
-        <v>14.285714285714</v>
+        <v>-7.017543859649</v>
       </c>
       <c r="I25" s="14">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="J25" s="14">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="K25" s="15">
-        <v>21.904761904761</v>
+        <v>12.096774193548</v>
       </c>
       <c r="L25" s="15">
-        <v>24.271844660194</v>
+        <v>15.833333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-44.444444444444</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F26" s="14">
+        <v>34</v>
+      </c>
+      <c r="G26" s="14">
         <v>30</v>
       </c>
-      <c r="G26" s="14">
-        <v>26</v>
-      </c>
       <c r="H26" s="15">
-        <v>15.384615384615</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J26" s="14">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="K26" s="15">
-        <v>12.280701754386</v>
+        <v>8.823529411764</v>
       </c>
       <c r="L26" s="15">
-        <v>10.344827586206</v>
+        <v>8.823529411764</v>
       </c>
       <c r="M26" s="15">
-        <v>-11.111111111111</v>
+        <v>-10.843373493975</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J28" s="14">
         <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>-70</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1557,17 +1557,17 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="14">
         <v>3</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="14">
-        <v>4</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-009pct.xlsx
+++ b/data/source/weekly/cs-en-us-009pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -881,8 +881,8 @@
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>-100</v>
       </c>
       <c r="N14" s="15">
         <v>-100</v>
@@ -901,8 +901,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -926,7 +926,7 @@
         <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
         <v>5</v>
@@ -952,22 +952,22 @@
         <v>-37.5</v>
       </c>
       <c r="I16" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" s="15">
-        <v>-40</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="L16" s="15">
-        <v>-52</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.826086956521</v>
+        <v>-48</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.156862745098</v>
+        <v>-92.073170731707</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
         <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>-11.111111111111</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="I17" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J17" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.631578947368</v>
+        <v>-2.439024390243</v>
       </c>
       <c r="L17" s="15">
-        <v>2.777777777777</v>
+        <v>8.108108108108</v>
       </c>
       <c r="M17" s="15">
-        <v>54.166666666666</v>
+        <v>48.148148148148</v>
       </c>
       <c r="N17" s="15">
-        <v>-61.052631578947</v>
+        <v>-61.165048543689</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>7</v>
-      </c>
       <c r="E18" s="15">
-        <v>-71.428571428571</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-68.75</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J18" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K18" s="15">
-        <v>-51.351351351351</v>
+        <v>-43.589743589743</v>
       </c>
       <c r="L18" s="15">
-        <v>-45.454545454545</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="M18" s="15">
-        <v>-68.421052631578</v>
+        <v>-64.516129032258</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.595375722543</v>
+        <v>-87.777777777777</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,63 +1057,63 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.222222222222</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F19" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G19" s="14">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.660377358490</v>
+        <v>-25</v>
       </c>
       <c r="I19" s="14">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="J19" s="14">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="K19" s="15">
-        <v>-15.384615384615</v>
+        <v>-21.088435374149</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.535211267605</v>
+        <v>-26.114649681528</v>
       </c>
       <c r="M19" s="15">
-        <v>-23.611111111111</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="N19" s="15">
-        <v>-58.174904942965</v>
+        <v>-59.298245614035</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
         <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
         <v>4</v>
@@ -1125,13 +1125,13 @@
         <v>-55.555555555555</v>
       </c>
       <c r="L20" s="15">
-        <v>33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="M20" s="15">
-        <v>-42.857142857142</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.918367346938</v>
+        <v>-96.078431372549</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.470588235294</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="F21" s="17">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G21" s="17">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.191919191919</v>
+        <v>-25.961538461538</v>
       </c>
       <c r="I21" s="17">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="J21" s="17">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.702127659574</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.966942148760</v>
+        <v>-24.427480916030</v>
       </c>
       <c r="M21" s="18">
-        <v>-28.125</v>
+        <v>-29.537366548042</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.796973518285</v>
+        <v>-76.623376623376</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>-12.5</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J23" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K23" s="15">
-        <v>-4.166666666666</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L23" s="15">
-        <v>91.666666666666</v>
+        <v>84.615384615384</v>
       </c>
       <c r="M23" s="15">
-        <v>9.523809523809</v>
+        <v>-4</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E24" s="15">
-        <v>-24.137931034482</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="F24" s="14">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="G24" s="14">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="H24" s="15">
-        <v>4.123711340206</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="I24" s="14">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="J24" s="14">
-        <v>250</v>
+        <v>286</v>
       </c>
       <c r="K24" s="15">
-        <v>3.2</v>
+        <v>-2.797202797202</v>
       </c>
       <c r="L24" s="15">
-        <v>11.688311688311</v>
+        <v>4.511278195488</v>
       </c>
       <c r="M24" s="15">
-        <v>-8.833922261484</v>
+        <v>-10.322580645161</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>-42.105263157894</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="G25" s="14">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H25" s="15">
-        <v>-7.017543859649</v>
+        <v>-43.076923076923</v>
       </c>
       <c r="I25" s="14">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J25" s="14">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="K25" s="15">
-        <v>12.096774193548</v>
+        <v>1.408450704225</v>
       </c>
       <c r="L25" s="15">
-        <v>15.833333333333</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>-9.090909090909</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F26" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G26" s="14">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H26" s="15">
+        <v>-10.256410256410</v>
+      </c>
+      <c r="I26" s="14">
+        <v>85</v>
+      </c>
+      <c r="J26" s="14">
+        <v>81</v>
+      </c>
+      <c r="K26" s="15">
+        <v>4.938271604938</v>
+      </c>
+      <c r="L26" s="15">
         <v>13.333333333333</v>
       </c>
-      <c r="I26" s="14">
-        <v>74</v>
-      </c>
-      <c r="J26" s="14">
-        <v>68</v>
-      </c>
-      <c r="K26" s="15">
-        <v>8.823529411764</v>
-      </c>
-      <c r="L26" s="15">
-        <v>8.823529411764</v>
-      </c>
       <c r="M26" s="15">
-        <v>-10.843373493975</v>
+        <v>-4.494382022471</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
       </c>
-      <c r="J27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>21</v>
+      <c r="J27" s="14">
+        <v>1</v>
+      </c>
+      <c r="K27" s="15">
+        <v>200</v>
       </c>
       <c r="L27" s="15">
         <v>-25</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
+        <v>4</v>
+      </c>
+      <c r="G28" s="14">
         <v>2</v>
       </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
         <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="L28" s="15">
-        <v>-50</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-009pct.xlsx
+++ b/data/source/weekly/cs-en-us-009pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -920,13 +920,13 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M15" s="15">
         <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>-66.666666666666</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -952,22 +952,22 @@
         <v>-37.5</v>
       </c>
       <c r="I16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K16" s="15">
-        <v>-38.095238095238</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L16" s="15">
-        <v>-50</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-48</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.073170731707</v>
+        <v>-92.178770949720</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
+        <v>200</v>
+      </c>
+      <c r="F17" s="14">
+        <v>15</v>
+      </c>
+      <c r="G17" s="14">
+        <v>17</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-11.764705882352</v>
+      </c>
+      <c r="I17" s="14">
+        <v>43</v>
+      </c>
+      <c r="J17" s="14">
+        <v>43</v>
+      </c>
+      <c r="K17" s="15">
         <v>0</v>
       </c>
-      <c r="F17" s="14">
-        <v>17</v>
-      </c>
-      <c r="G17" s="14">
-        <v>18</v>
-      </c>
-      <c r="H17" s="15">
-        <v>-5.555555555555</v>
-      </c>
-      <c r="I17" s="14">
-        <v>40</v>
-      </c>
-      <c r="J17" s="14">
-        <v>41</v>
-      </c>
-      <c r="K17" s="15">
-        <v>-2.439024390243</v>
-      </c>
       <c r="L17" s="15">
-        <v>8.108108108108</v>
+        <v>7.5</v>
       </c>
       <c r="M17" s="15">
-        <v>48.148148148148</v>
+        <v>26.470588235294</v>
       </c>
       <c r="N17" s="15">
-        <v>-61.165048543689</v>
+        <v>-61.607142857142</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F18" s="14">
         <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.857142857142</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I18" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J18" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>-43.589743589743</v>
+        <v>-37.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-35.294117647058</v>
+        <v>-37.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-64.516129032258</v>
+        <v>-63.235294117647</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.777777777777</v>
+        <v>-87.244897959183</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
         <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-58.823529411764</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F19" s="14">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H19" s="15">
-        <v>-25</v>
+        <v>-34.328358208955</v>
       </c>
       <c r="I19" s="14">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="J19" s="14">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K19" s="15">
-        <v>-21.088435374149</v>
+        <v>-20.731707317073</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.114649681528</v>
+        <v>-18.75</v>
       </c>
       <c r="M19" s="15">
-        <v>-25.641025641025</v>
+        <v>-27.374301675977</v>
       </c>
       <c r="N19" s="15">
-        <v>-59.298245614035</v>
+        <v>-58.466453674121</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1110,10 +1110,10 @@
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
         <v>4</v>
@@ -1128,10 +1128,10 @@
         <v>-20</v>
       </c>
       <c r="M20" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.078431372549</v>
+        <v>-96.460176991150</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-39.130434782608</v>
+        <v>5</v>
       </c>
       <c r="F21" s="17">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.961538461538</v>
+        <v>-30.841121495327</v>
       </c>
       <c r="I21" s="17">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="J21" s="17">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.255813953488</v>
+        <v>-21.505376344086</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.427480916030</v>
+        <v>-22.064056939501</v>
       </c>
       <c r="M21" s="18">
-        <v>-29.537366548042</v>
+        <v>-31.5625</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.623376623376</v>
+        <v>-76.375404530744</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>-75</v>
       </c>
       <c r="M22" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-50</v>
+        <v>3</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G23" s="14">
         <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J23" s="14">
         <v>26</v>
       </c>
       <c r="K23" s="15">
-        <v>-7.692307692307</v>
+        <v>3.846153846153</v>
       </c>
       <c r="L23" s="15">
-        <v>84.615384615384</v>
+        <v>107.692307692308</v>
       </c>
       <c r="M23" s="15">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>-38.888888888888</v>
+        <v>-20</v>
       </c>
       <c r="F24" s="14">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G24" s="14">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H24" s="15">
-        <v>-18.918918918918</v>
+        <v>-22.123893805309</v>
       </c>
       <c r="I24" s="14">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="J24" s="14">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.797202797202</v>
+        <v>-4.430379746835</v>
       </c>
       <c r="L24" s="15">
-        <v>4.511278195488</v>
+        <v>1.342281879194</v>
       </c>
       <c r="M24" s="15">
-        <v>-10.322580645161</v>
+        <v>-10.385756676557</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="F25" s="14">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G25" s="14">
         <v>65</v>
       </c>
       <c r="H25" s="15">
-        <v>-43.076923076923</v>
+        <v>-49.230769230769</v>
       </c>
       <c r="I25" s="14">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="J25" s="14">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="K25" s="15">
-        <v>1.408450704225</v>
+        <v>-2.515723270440</v>
       </c>
       <c r="L25" s="15">
-        <v>6.666666666666</v>
+        <v>-1.898734177215</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-15.384615384615</v>
+        <v>116.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G26" s="14">
         <v>39</v>
       </c>
       <c r="H26" s="15">
-        <v>-10.256410256410</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="J26" s="14">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K26" s="15">
-        <v>4.938271604938</v>
+        <v>13.953488372093</v>
       </c>
       <c r="L26" s="15">
-        <v>13.333333333333</v>
+        <v>19.512195121951</v>
       </c>
       <c r="M26" s="15">
-        <v>-4.494382022471</v>
+        <v>-1.010101010101</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>200</v>
       </c>
       <c r="L27" s="15">
-        <v>-25</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>-30</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L28" s="15">
-        <v>-36.363636363636</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1493,8 +1493,8 @@
       <c r="K29" s="15">
         <v>-100</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="15">
+        <v>-100</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
@@ -1534,8 +1534,8 @@
       <c r="K30" s="15">
         <v>-100</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="15">
+        <v>-100</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-009pct.xlsx
+++ b/data/source/weekly/cs-en-us-009pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -926,7 +926,7 @@
         <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>-70</v>
+        <v>-76.923076923076</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
+        <v>100</v>
+      </c>
+      <c r="F16" s="14">
+        <v>6</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="15">
         <v>0</v>
       </c>
-      <c r="F16" s="14">
-        <v>5</v>
-      </c>
-      <c r="G16" s="14">
-        <v>8</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-37.5</v>
-      </c>
       <c r="I16" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J16" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>-36.363636363636</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="L16" s="15">
-        <v>-53.333333333333</v>
+        <v>-51.515151515151</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.148148148148</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.178770949720</v>
+        <v>-92.270531400966</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
+        <v>16</v>
+      </c>
+      <c r="G17" s="14">
         <v>15</v>
       </c>
-      <c r="G17" s="14">
-        <v>17</v>
-      </c>
       <c r="H17" s="15">
-        <v>-11.764705882352</v>
+        <v>6.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J17" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>-4.081632653061</v>
       </c>
       <c r="L17" s="15">
-        <v>7.5</v>
+        <v>11.904761904761</v>
       </c>
       <c r="M17" s="15">
-        <v>26.470588235294</v>
+        <v>27.027027027027</v>
       </c>
       <c r="N17" s="15">
-        <v>-61.607142857142</v>
+        <v>-61.788617886178</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E18" s="15">
-        <v>200</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="H18" s="15">
-        <v>-38.461538461538</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I18" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="K18" s="15">
-        <v>-37.5</v>
+        <v>-44.230769230769</v>
       </c>
       <c r="L18" s="15">
-        <v>-37.5</v>
+        <v>-30.952380952381</v>
       </c>
       <c r="M18" s="15">
-        <v>-63.235294117647</v>
+        <v>-57.352941176470</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.244897959183</v>
+        <v>-86.757990867579</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E19" s="15">
-        <v>-17.647058823529</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
         <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H19" s="15">
-        <v>-34.328358208955</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="I19" s="14">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="J19" s="14">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="K19" s="15">
-        <v>-20.731707317073</v>
+        <v>-24.456521739130</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.75</v>
+        <v>-19.653179190751</v>
       </c>
       <c r="M19" s="15">
-        <v>-27.374301675977</v>
+        <v>-27.979274611399</v>
       </c>
       <c r="N19" s="15">
-        <v>-58.466453674121</v>
+        <v>-59.710144927536</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
+        <v>1</v>
+      </c>
+      <c r="G20" s="14">
         <v>2</v>
       </c>
-      <c r="G20" s="14">
-        <v>1</v>
-      </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
         <v>4</v>
       </c>
       <c r="J20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K20" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="L20" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.460176991150</v>
+        <v>-96.694214876033</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>5</v>
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G21" s="17">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H21" s="18">
-        <v>-30.841121495327</v>
+        <v>-32.478632478632</v>
       </c>
       <c r="I21" s="17">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="J21" s="17">
-        <v>279</v>
+        <v>319</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.505376344086</v>
+        <v>-25.391849529780</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.064056939501</v>
+        <v>-21.192052980132</v>
       </c>
       <c r="M21" s="18">
-        <v>-31.5625</v>
+        <v>-30.205278592375</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.375404530744</v>
+        <v>-76.937984496124</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
+        <v>4</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-75</v>
       </c>
       <c r="F23" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J23" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K23" s="15">
-        <v>3.846153846153</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>107.692307692308</v>
+        <v>100</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>3.703703703703</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>23</v>
+      </c>
+      <c r="D24" s="14">
         <v>24</v>
       </c>
-      <c r="D24" s="14">
-        <v>30</v>
-      </c>
       <c r="E24" s="15">
-        <v>-20</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G24" s="14">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H24" s="15">
-        <v>-22.123893805309</v>
+        <v>-24.369747899159</v>
       </c>
       <c r="I24" s="14">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="J24" s="14">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="K24" s="15">
-        <v>-4.430379746835</v>
+        <v>-4.411764705882</v>
       </c>
       <c r="L24" s="15">
-        <v>1.342281879194</v>
+        <v>1.880877742946</v>
       </c>
       <c r="M24" s="15">
-        <v>-10.385756676557</v>
+        <v>-14.473684210526</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
         <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-35.294117647058</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="F25" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G25" s="14">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="H25" s="15">
-        <v>-49.230769230769</v>
+        <v>-49.295774647887</v>
       </c>
       <c r="I25" s="14">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J25" s="14">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="K25" s="15">
-        <v>-2.515723270440</v>
+        <v>-6.818181818181</v>
       </c>
       <c r="L25" s="15">
-        <v>-1.898734177215</v>
+        <v>-2.958579881656</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
         <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>116.666666666667</v>
+        <v>150</v>
       </c>
       <c r="F26" s="14">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G26" s="14">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>36.111111111111</v>
       </c>
       <c r="I26" s="14">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="J26" s="14">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K26" s="15">
-        <v>13.953488372093</v>
+        <v>22.826086956521</v>
       </c>
       <c r="L26" s="15">
-        <v>19.512195121951</v>
+        <v>20.212765957446</v>
       </c>
       <c r="M26" s="15">
-        <v>-1.010101010101</v>
+        <v>6.603773584905</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>150</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>-27.272727272727</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L28" s="15">
-        <v>-38.461538461538</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>4</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>300</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-009pct.xlsx
+++ b/data/source/weekly/cs-en-us-009pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -920,7 +920,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M15" s="15">
         <v>200</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
         <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J16" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>-30.434782608695</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="L16" s="15">
-        <v>-51.515151515151</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="15">
-        <v>-44.827586206896</v>
+        <v>-46.875</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.270531400966</v>
+        <v>-92.444444444444</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H17" s="15">
-        <v>6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J17" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.081632653061</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="L17" s="15">
-        <v>11.904761904761</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M17" s="15">
-        <v>27.027027027027</v>
+        <v>25</v>
       </c>
       <c r="N17" s="15">
-        <v>-61.788617886178</v>
+        <v>-61.538461538461</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>5</v>
+      </c>
+      <c r="D18" s="14">
         <v>4</v>
       </c>
-      <c r="D18" s="14">
-        <v>12</v>
-      </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-45.454545454545</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J18" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K18" s="15">
-        <v>-44.230769230769</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="L18" s="15">
-        <v>-30.952380952381</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="M18" s="15">
-        <v>-57.352941176470</v>
+        <v>-51.428571428571</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.757990867579</v>
+        <v>-85.152838427947</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D19" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F19" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
         <v>72</v>
       </c>
       <c r="H19" s="15">
-        <v>-38.888888888888</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="J19" s="14">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="K19" s="15">
-        <v>-24.456521739130</v>
+        <v>-22.772277227722</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.653179190751</v>
+        <v>-17.894736842105</v>
       </c>
       <c r="M19" s="15">
-        <v>-27.979274611399</v>
+        <v>-24.637681159420</v>
       </c>
       <c r="N19" s="15">
-        <v>-59.710144927536</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1106,32 +1106,32 @@
       <c r="E20" s="15">
         <v>-100</v>
       </c>
-      <c r="F20" s="14">
-        <v>1</v>
+      <c r="F20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G20" s="14">
         <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="14">
         <v>4</v>
       </c>
       <c r="J20" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K20" s="15">
-        <v>-60</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M20" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.694214876033</v>
+        <v>-96.825396825396</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="F21" s="17">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G21" s="17">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H21" s="18">
-        <v>-32.478632478632</v>
+        <v>-27.678571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="J21" s="17">
-        <v>319</v>
+        <v>348</v>
       </c>
       <c r="K21" s="18">
-        <v>-25.391849529780</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.192052980132</v>
+        <v>-19.018404907975</v>
       </c>
       <c r="M21" s="18">
-        <v>-30.205278592375</v>
+        <v>-27.671232876712</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.937984496124</v>
+        <v>-75.802016498625</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>1</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>-75</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G23" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="I23" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J23" s="14">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K23" s="15">
-        <v>-6.666666666666</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="L23" s="15">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="M23" s="15">
-        <v>3.703703703703</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="E24" s="15">
-        <v>-4.166666666666</v>
+        <v>-27.027027027027</v>
       </c>
       <c r="F24" s="14">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G24" s="14">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H24" s="15">
-        <v>-24.369747899159</v>
+        <v>-24.409448818897</v>
       </c>
       <c r="I24" s="14">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="J24" s="14">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="K24" s="15">
-        <v>-4.411764705882</v>
+        <v>-6.631299734748</v>
       </c>
       <c r="L24" s="15">
-        <v>1.880877742946</v>
+        <v>3.225806451612</v>
       </c>
       <c r="M24" s="15">
-        <v>-14.473684210526</v>
+        <v>-12.655086848635</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>-47.058823529411</v>
+        <v>5.555555555555</v>
       </c>
       <c r="F25" s="14">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G25" s="14">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H25" s="15">
-        <v>-49.295774647887</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I25" s="14">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="J25" s="14">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.818181818181</v>
+        <v>-5.670103092783</v>
       </c>
       <c r="L25" s="15">
-        <v>-2.958579881656</v>
+        <v>3.977272727272</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
         <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H26" s="15">
-        <v>36.111111111111</v>
+        <v>45.161290322580</v>
       </c>
       <c r="I26" s="14">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="J26" s="14">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K26" s="15">
-        <v>22.826086956521</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L26" s="15">
-        <v>20.212765957446</v>
+        <v>22.680412371134</v>
       </c>
       <c r="M26" s="15">
-        <v>6.603773584905</v>
+        <v>1.709401709401</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1412,7 +1412,7 @@
         <v>200</v>
       </c>
       <c r="L27" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>166.666666666667</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
         <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>-15.384615384615</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L28" s="15">
-        <v>-21.428571428571</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-009pct.xlsx
+++ b/data/source/weekly/cs-en-us-009pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,8 +901,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -911,7 +911,7 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>20</v>
@@ -920,13 +920,13 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>-57.142857142857</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-76.923076923076</v>
+        <v>-69.230769230769</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -946,28 +946,28 @@
         <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-16.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="I16" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J16" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K16" s="15">
-        <v>-34.615384615384</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="L16" s="15">
+        <v>-52.631578947368</v>
+      </c>
+      <c r="M16" s="15">
         <v>-50</v>
       </c>
-      <c r="M16" s="15">
-        <v>-46.875</v>
-      </c>
       <c r="N16" s="15">
-        <v>-92.444444444444</v>
+        <v>-92.622950819672</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I17" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J17" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.846153846153</v>
+        <v>1.886792452830</v>
       </c>
       <c r="L17" s="15">
-        <v>11.111111111111</v>
+        <v>12.5</v>
       </c>
       <c r="M17" s="15">
-        <v>25</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N17" s="15">
-        <v>-61.538461538461</v>
+        <v>-61.971830985915</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
         <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-21.052631578947</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J18" s="14">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K18" s="15">
-        <v>-39.285714285714</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-20.930232558139</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M18" s="15">
-        <v>-51.428571428571</v>
+        <v>-47.222222222222</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.152838427947</v>
+        <v>-84.033613445378</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-5.555555555555</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G19" s="14">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H19" s="15">
-        <v>-33.333333333333</v>
+        <v>-24.285714285714</v>
       </c>
       <c r="I19" s="14">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="J19" s="14">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="K19" s="15">
-        <v>-22.772277227722</v>
+        <v>-23.041474654377</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.894736842105</v>
+        <v>-16.915422885572</v>
       </c>
       <c r="M19" s="15">
-        <v>-24.637681159420</v>
+        <v>-24.434389140271</v>
       </c>
       <c r="N19" s="15">
-        <v>-57.142857142857</v>
+        <v>-57.614213197969</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,11 +1100,11 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>20</v>
@@ -1128,10 +1128,10 @@
         <v>-42.857142857142</v>
       </c>
       <c r="M20" s="15">
-        <v>-71.428571428571</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.825396825396</v>
+        <v>-97.037037037037</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-10.344827586206</v>
+        <v>-5</v>
       </c>
       <c r="F21" s="17">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G21" s="17">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H21" s="18">
-        <v>-27.678571428571</v>
+        <v>-19.266055045871</v>
       </c>
       <c r="I21" s="17">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="J21" s="17">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="K21" s="18">
-        <v>-24.137931034482</v>
+        <v>-22.554347826087</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.018404907975</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="M21" s="18">
-        <v>-27.671232876712</v>
+        <v>-26.735218508997</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.802016498625</v>
+        <v>-75.641025641025</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>5</v>
+      </c>
+      <c r="D23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="14">
-        <v>7</v>
-      </c>
       <c r="E23" s="15">
-        <v>-71.428571428571</v>
+        <v>150</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
         <v>13</v>
       </c>
       <c r="H23" s="15">
-        <v>-46.153846153846</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I23" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J23" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K23" s="15">
-        <v>-18.918918918918</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L23" s="15">
-        <v>87.5</v>
+        <v>111.764705882353</v>
       </c>
       <c r="M23" s="15">
-        <v>11.111111111111</v>
+        <v>24.137931034482</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="E24" s="15">
-        <v>-27.027027027027</v>
+        <v>-55.357142857142</v>
       </c>
       <c r="F24" s="14">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G24" s="14">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="H24" s="15">
-        <v>-24.409448818897</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="J24" s="14">
-        <v>377</v>
+        <v>433</v>
       </c>
       <c r="K24" s="15">
-        <v>-6.631299734748</v>
+        <v>-13.163972286374</v>
       </c>
       <c r="L24" s="15">
-        <v>3.225806451612</v>
+        <v>3.296703296703</v>
       </c>
       <c r="M24" s="15">
-        <v>-12.655086848635</v>
+        <v>-13.563218390804</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E25" s="15">
-        <v>5.555555555555</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="F25" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G25" s="14">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H25" s="15">
-        <v>-35.714285714285</v>
+        <v>-41.025641025641</v>
       </c>
       <c r="I25" s="14">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="J25" s="14">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="K25" s="15">
-        <v>-5.670103092783</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="L25" s="15">
-        <v>3.977272727272</v>
+        <v>1.604278074866</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="F26" s="14">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G26" s="14">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H26" s="15">
-        <v>45.161290322580</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I26" s="14">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J26" s="14">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="K26" s="15">
-        <v>21.428571428571</v>
+        <v>15.740740740740</v>
       </c>
       <c r="L26" s="15">
-        <v>22.680412371134</v>
+        <v>21.359223300970</v>
       </c>
       <c r="M26" s="15">
-        <v>1.709401709401</v>
+        <v>-0.793650793650</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="14">
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="H27" s="15">
-        <v>-100</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
         <v>1</v>
       </c>
       <c r="K27" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L27" s="15">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>133.333333333333</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
         <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>-7.692307692307</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L28" s="15">
         <v>-33.333333333333</v>

--- a/data/source/weekly/cs-en-us-009pct.xlsx
+++ b/data/source/weekly/cs-en-us-009pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -892,123 +892,123 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
-      <c r="J15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>21</v>
+      <c r="J15" s="14">
+        <v>1</v>
+      </c>
+      <c r="K15" s="15">
+        <v>300</v>
       </c>
       <c r="L15" s="15">
         <v>-42.857142857142</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-69.230769230769</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F16" s="14">
+        <v>4</v>
+      </c>
+      <c r="G16" s="14">
+        <v>12</v>
+      </c>
+      <c r="H16" s="15">
         <v>-66.666666666666</v>
-      </c>
-      <c r="F16" s="14">
-        <v>5</v>
-      </c>
-      <c r="G16" s="14">
-        <v>8</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-37.5</v>
       </c>
       <c r="I16" s="14">
         <v>18</v>
       </c>
       <c r="J16" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>-37.931034482758</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="L16" s="15">
         <v>-52.631578947368</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-55</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.622950819672</v>
+        <v>-93.233082706766</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
-        <v>3</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="14">
+        <v>12</v>
+      </c>
+      <c r="G17" s="14">
         <v>14</v>
       </c>
-      <c r="G17" s="14">
-        <v>11</v>
-      </c>
       <c r="H17" s="15">
-        <v>27.272727272727</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I17" s="14">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J17" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K17" s="15">
-        <v>1.886792452830</v>
+        <v>-3.508771929824</v>
       </c>
       <c r="L17" s="15">
-        <v>12.5</v>
+        <v>7.843137254901</v>
       </c>
       <c r="M17" s="15">
-        <v>28.571428571428</v>
+        <v>22.222222222222</v>
       </c>
       <c r="N17" s="15">
-        <v>-61.971830985915</v>
+        <v>-63.087248322147</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
         <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-16.666666666666</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="I18" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J18" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K18" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.508474576271</v>
       </c>
       <c r="L18" s="15">
-        <v>-13.636363636363</v>
+        <v>-12.765957446808</v>
       </c>
       <c r="M18" s="15">
-        <v>-47.222222222222</v>
+        <v>-46.753246753246</v>
       </c>
       <c r="N18" s="15">
-        <v>-84.033613445378</v>
+        <v>-83.6</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,78 +1060,78 @@
         <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F19" s="14">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G19" s="14">
         <v>70</v>
       </c>
       <c r="H19" s="15">
-        <v>-24.285714285714</v>
+        <v>-27.142857142857</v>
       </c>
       <c r="I19" s="14">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="J19" s="14">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="K19" s="15">
-        <v>-23.041474654377</v>
+        <v>-23.504273504273</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.915422885572</v>
+        <v>-15.566037735849</v>
       </c>
       <c r="M19" s="15">
-        <v>-24.434389140271</v>
+        <v>-24.152542372881</v>
       </c>
       <c r="N19" s="15">
-        <v>-57.614213197969</v>
+        <v>-57.279236276849</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>1</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K20" s="15">
-        <v>-63.636363636363</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-42.857142857142</v>
+        <v>-37.5</v>
       </c>
       <c r="M20" s="15">
-        <v>-73.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.037037037037</v>
+        <v>-96.732026143790</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>-5</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G21" s="17">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.266055045871</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I21" s="17">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="J21" s="17">
-        <v>368</v>
+        <v>398</v>
       </c>
       <c r="K21" s="18">
-        <v>-22.554347826087</v>
+        <v>-24.120603015075</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.391304347826</v>
+        <v>-16.804407713498</v>
       </c>
       <c r="M21" s="18">
-        <v>-26.735218508997</v>
+        <v>-27.577937649880</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.641025641025</v>
+        <v>-75.936254980079</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>5</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>150</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>-7.692307692307</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I23" s="14">
         <v>36</v>
       </c>
       <c r="J23" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K23" s="15">
-        <v>-7.692307692307</v>
+        <v>-10</v>
       </c>
       <c r="L23" s="15">
         <v>111.764705882353</v>
       </c>
       <c r="M23" s="15">
-        <v>24.137931034482</v>
+        <v>9.090909090909</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D24" s="14">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E24" s="15">
-        <v>-55.357142857142</v>
+        <v>-7.317073170731</v>
       </c>
       <c r="F24" s="14">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="G24" s="14">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="H24" s="15">
-        <v>-33.333333333333</v>
+        <v>-28.481012658227</v>
       </c>
       <c r="I24" s="14">
-        <v>376</v>
+        <v>415</v>
       </c>
       <c r="J24" s="14">
-        <v>433</v>
+        <v>474</v>
       </c>
       <c r="K24" s="15">
-        <v>-13.163972286374</v>
+        <v>-12.447257383966</v>
       </c>
       <c r="L24" s="15">
-        <v>3.296703296703</v>
+        <v>6.138107416879</v>
       </c>
       <c r="M24" s="15">
-        <v>-13.563218390804</v>
+        <v>-10.173160173160</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D25" s="14">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-76.923076923076</v>
+        <v>52.941176470588</v>
       </c>
       <c r="F25" s="14">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G25" s="14">
         <v>78</v>
       </c>
       <c r="H25" s="15">
-        <v>-41.025641025641</v>
+        <v>-21.794871794871</v>
       </c>
       <c r="I25" s="14">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="J25" s="14">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="K25" s="15">
-        <v>-13.636363636363</v>
+        <v>-8.860759493670</v>
       </c>
       <c r="L25" s="15">
-        <v>1.604278074866</v>
+        <v>4.854368932038</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-30</v>
+        <v>25</v>
       </c>
       <c r="F26" s="14">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G26" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H26" s="15">
-        <v>42.857142857142</v>
+        <v>20</v>
       </c>
       <c r="I26" s="14">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="J26" s="14">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="K26" s="15">
-        <v>15.740740740740</v>
+        <v>15.517241379310</v>
       </c>
       <c r="L26" s="15">
-        <v>21.359223300970</v>
+        <v>18.584070796460</v>
       </c>
       <c r="M26" s="15">
-        <v>-0.793650793650</v>
+        <v>-5.633802816901</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
         <v>-50</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>25</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
         <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>-14.285714285714</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L28" s="15">
-        <v>-33.333333333333</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-009pct.xlsx
+++ b/data/source/weekly/cs-en-us-009pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,23 +869,23 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -933,82 +933,82 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
         <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>-47.058823529411</v>
+        <v>-45.714285714285</v>
       </c>
       <c r="L16" s="15">
-        <v>-52.631578947368</v>
+        <v>-51.282051282051</v>
       </c>
       <c r="M16" s="15">
-        <v>-55</v>
+        <v>-57.777777777777</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.233082706766</v>
+        <v>-92.988929889298</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="14">
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>-100</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F17" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>-14.285714285714</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J17" s="14">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.508771929824</v>
+        <v>-9.375</v>
       </c>
       <c r="L17" s="15">
-        <v>7.843137254901</v>
+        <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>22.222222222222</v>
+        <v>28.888888888888</v>
       </c>
       <c r="N17" s="15">
-        <v>-63.087248322147</v>
+        <v>-63.975155279503</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-21.052631578947</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I18" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J18" s="14">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K18" s="15">
-        <v>-30.508474576271</v>
+        <v>-31.746031746031</v>
       </c>
       <c r="L18" s="15">
-        <v>-12.765957446808</v>
+        <v>-17.307692307692</v>
       </c>
       <c r="M18" s="15">
-        <v>-46.753246753246</v>
+        <v>-48.809523809523</v>
       </c>
       <c r="N18" s="15">
-        <v>-83.6</v>
+        <v>-83.268482490272</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>-29.411764705882</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="F19" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G19" s="14">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H19" s="15">
-        <v>-27.142857142857</v>
+        <v>-22.058823529411</v>
       </c>
       <c r="I19" s="14">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="J19" s="14">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="K19" s="15">
-        <v>-23.504273504273</v>
+        <v>-24.206349206349</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.566037735849</v>
+        <v>-15.859030837004</v>
       </c>
       <c r="M19" s="15">
-        <v>-24.152542372881</v>
+        <v>-23.6</v>
       </c>
       <c r="N19" s="15">
-        <v>-57.279236276849</v>
+        <v>-58.205689277899</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
+        <v>2</v>
+      </c>
+      <c r="G20" s="14">
+        <v>2</v>
+      </c>
+      <c r="H20" s="15">
         <v>0</v>
       </c>
-      <c r="F20" s="14">
-        <v>1</v>
-      </c>
-      <c r="G20" s="14">
-        <v>3</v>
-      </c>
-      <c r="H20" s="15">
-        <v>-66.666666666666</v>
-      </c>
       <c r="I20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20" s="14">
         <v>12</v>
       </c>
       <c r="K20" s="15">
-        <v>-58.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L20" s="15">
-        <v>-37.5</v>
+        <v>-40</v>
       </c>
       <c r="M20" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.732026143790</v>
+        <v>-96.226415094339</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
         <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>-46.666666666666</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="F21" s="17">
         <v>84</v>
       </c>
       <c r="G21" s="17">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="H21" s="18">
-        <v>-29.411764705882</v>
+        <v>-22.935779816513</v>
       </c>
       <c r="I21" s="17">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="J21" s="17">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="K21" s="18">
-        <v>-24.120603015075</v>
+        <v>-24.766355140186</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.804407713498</v>
+        <v>-18.066157760814</v>
       </c>
       <c r="M21" s="18">
-        <v>-27.577937649880</v>
+        <v>-27.477477477477</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.936254980079</v>
+        <v>-75.661375661375</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="L22" s="15">
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="M22" s="15">
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
         <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>-35.714285714285</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I23" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J23" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K23" s="15">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L23" s="15">
-        <v>111.764705882353</v>
+        <v>100</v>
       </c>
       <c r="M23" s="15">
-        <v>9.090909090909</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D24" s="14">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-7.317073170731</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F24" s="14">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="G24" s="14">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H24" s="15">
-        <v>-28.481012658227</v>
+        <v>-23.125</v>
       </c>
       <c r="I24" s="14">
-        <v>415</v>
+        <v>448</v>
       </c>
       <c r="J24" s="14">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="K24" s="15">
-        <v>-12.447257383966</v>
+        <v>-10.4</v>
       </c>
       <c r="L24" s="15">
-        <v>6.138107416879</v>
+        <v>5.411764705882</v>
       </c>
       <c r="M24" s="15">
-        <v>-10.173160173160</v>
+        <v>-7.628865979381</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>52.941176470588</v>
+        <v>114.285714285714</v>
       </c>
       <c r="F25" s="14">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G25" s="14">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="H25" s="15">
-        <v>-21.794871794871</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="J25" s="14">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="K25" s="15">
-        <v>-8.860759493670</v>
+        <v>-4.918032786885</v>
       </c>
       <c r="L25" s="15">
-        <v>4.854368932038</v>
+        <v>0.432900432900</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>20</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="I26" s="14">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="J26" s="14">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="K26" s="15">
-        <v>15.517241379310</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L26" s="15">
-        <v>18.584070796460</v>
+        <v>24.137931034482</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.633802816901</v>
+        <v>-0.689655172413</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,13 +1435,13 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>133.333333333333</v>
+        <v>300</v>
       </c>
       <c r="I28" s="14">
         <v>15</v>
@@ -1453,7 +1453,7 @@
         <v>7.142857142857</v>
       </c>
       <c r="L28" s="15">
-        <v>-21.052631578947</v>
+        <v>-25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,31 +1484,31 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="M29" s="15">
+        <v>100</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,23 +1525,23 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="M30" s="15">
+        <v>0</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>4</v>

--- a/data/source/weekly/cs-en-us-009pct.xlsx
+++ b/data/source/weekly/cs-en-us-009pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -895,38 +895,38 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>300</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="M15" s="15">
         <v>33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-71.428571428571</v>
+        <v>-73.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
         <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15">
-        <v>-75</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J16" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K16" s="15">
-        <v>-45.714285714285</v>
+        <v>-41.025641025641</v>
       </c>
       <c r="L16" s="15">
-        <v>-51.282051282051</v>
+        <v>-43.902439024390</v>
       </c>
       <c r="M16" s="15">
-        <v>-57.777777777777</v>
+        <v>-53.061224489795</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.988929889298</v>
+        <v>-91.843971631205</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-57.142857142857</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>-26.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="I17" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J17" s="14">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K17" s="15">
-        <v>-9.375</v>
+        <v>-10.294117647058</v>
       </c>
       <c r="L17" s="15">
-        <v>0</v>
+        <v>-4.6875</v>
       </c>
       <c r="M17" s="15">
-        <v>28.888888888888</v>
+        <v>19.607843137254</v>
       </c>
       <c r="N17" s="15">
-        <v>-63.975155279503</v>
+        <v>-65.142857142857</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14">
-        <v>4</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-50</v>
+        <v>7</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>18.181818181818</v>
+        <v>100</v>
       </c>
       <c r="I18" s="14">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J18" s="14">
         <v>63</v>
       </c>
       <c r="K18" s="15">
-        <v>-31.746031746031</v>
+        <v>-20.634920634920</v>
       </c>
       <c r="L18" s="15">
-        <v>-17.307692307692</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="M18" s="15">
-        <v>-48.809523809523</v>
+        <v>-43.820224719101</v>
       </c>
       <c r="N18" s="15">
-        <v>-83.268482490272</v>
+        <v>-81.412639405204</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-38.888888888888</v>
+        <v>61.538461538461</v>
       </c>
       <c r="F19" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G19" s="14">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H19" s="15">
-        <v>-22.058823529411</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I19" s="14">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="J19" s="14">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="K19" s="15">
-        <v>-24.206349206349</v>
+        <v>-19.245283018867</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.859030837004</v>
+        <v>-10.460251046025</v>
       </c>
       <c r="M19" s="15">
-        <v>-23.6</v>
+        <v>-17.054263565891</v>
       </c>
       <c r="N19" s="15">
-        <v>-58.205689277899</v>
+        <v>-55.509355509355</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
         <v>6</v>
       </c>
       <c r="J20" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K20" s="15">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="L20" s="15">
         <v>-50</v>
-      </c>
-      <c r="L20" s="15">
-        <v>-40</v>
       </c>
       <c r="M20" s="15">
         <v>-60</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.226415094339</v>
+        <v>-96.491228070175</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-36.666666666666</v>
+        <v>44</v>
       </c>
       <c r="F21" s="17">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G21" s="17">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.935779816513</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I21" s="17">
-        <v>322</v>
+        <v>359</v>
       </c>
       <c r="J21" s="17">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="K21" s="18">
-        <v>-24.766355140186</v>
+        <v>-20.750551876379</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.066157760814</v>
+        <v>-14.523809523809</v>
       </c>
       <c r="M21" s="18">
-        <v>-27.477477477477</v>
+        <v>-23.126338329764</v>
       </c>
       <c r="N21" s="18">
-        <v>-75.661375661375</v>
+        <v>-74.302075876879</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
         <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F23" s="14">
+        <v>9</v>
+      </c>
+      <c r="G23" s="14">
+        <v>9</v>
+      </c>
+      <c r="H23" s="15">
         <v>0</v>
-      </c>
-      <c r="F23" s="14">
-        <v>12</v>
-      </c>
-      <c r="G23" s="14">
-        <v>14</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-14.285714285714</v>
       </c>
       <c r="I23" s="14">
         <v>40</v>
       </c>
       <c r="J23" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K23" s="15">
-        <v>-9.090909090909</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="L23" s="15">
-        <v>100</v>
+        <v>73.913043478260</v>
       </c>
       <c r="M23" s="15">
-        <v>14.285714285714</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E24" s="15">
-        <v>23.076923076923</v>
+        <v>-36.585365853658</v>
       </c>
       <c r="F24" s="14">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G24" s="14">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H24" s="15">
-        <v>-23.125</v>
+        <v>-25.609756097561</v>
       </c>
       <c r="I24" s="14">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="J24" s="14">
-        <v>500</v>
+        <v>541</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.4</v>
+        <v>-12.569316081330</v>
       </c>
       <c r="L24" s="15">
-        <v>5.411764705882</v>
+        <v>0.852878464818</v>
       </c>
       <c r="M24" s="15">
-        <v>-7.628865979381</v>
+        <v>-7.797270955165</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E25" s="15">
-        <v>114.285714285714</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="F25" s="14">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G25" s="14">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>-10.958904109589</v>
       </c>
       <c r="I25" s="14">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="J25" s="14">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="K25" s="15">
-        <v>-4.918032786885</v>
+        <v>-6.367041198501</v>
       </c>
       <c r="L25" s="15">
-        <v>0.432900432900</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
         <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
         <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.823529411764</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I26" s="14">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J26" s="14">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="K26" s="15">
-        <v>14.285714285714</v>
+        <v>13.636363636363</v>
       </c>
       <c r="L26" s="15">
-        <v>24.137931034482</v>
+        <v>26.050420168067</v>
       </c>
       <c r="M26" s="15">
-        <v>-0.689655172413</v>
+        <v>0.671140939597</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1444,16 +1444,16 @@
         <v>300</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
         <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>7.142857142857</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-009pct.xlsx
+++ b/data/source/weekly/cs-en-us-009pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -896,28 +896,28 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
         <v>-50</v>
@@ -926,7 +926,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-73.333333333333</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
-      </c>
-      <c r="D16" s="14">
-        <v>4</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-53.846153846153</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" s="14">
         <v>39</v>
       </c>
       <c r="K16" s="15">
-        <v>-41.025641025641</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L16" s="15">
-        <v>-43.902439024390</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.061224489795</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.843971631205</v>
+        <v>-91.891891891891</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-25</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H17" s="15">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="J17" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.294117647058</v>
+        <v>-6.756756756756</v>
       </c>
       <c r="L17" s="15">
-        <v>-4.6875</v>
+        <v>4.545454545454</v>
       </c>
       <c r="M17" s="15">
-        <v>19.607843137254</v>
+        <v>30.188679245283</v>
       </c>
       <c r="N17" s="15">
-        <v>-65.142857142857</v>
+        <v>-63.101604278074</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>7</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
         <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>100</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I18" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J18" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K18" s="15">
-        <v>-20.634920634920</v>
+        <v>-20.3125</v>
       </c>
       <c r="L18" s="15">
-        <v>-10.714285714285</v>
+        <v>-12.068965517241</v>
       </c>
       <c r="M18" s="15">
-        <v>-43.820224719101</v>
+        <v>-44.565217391304</v>
       </c>
       <c r="N18" s="15">
-        <v>-81.412639405204</v>
+        <v>-82.167832167832</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>61.538461538461</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G19" s="14">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H19" s="15">
-        <v>-11.111111111111</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I19" s="14">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="J19" s="14">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="K19" s="15">
-        <v>-19.245283018867</v>
+        <v>-20.848056537102</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.460251046025</v>
+        <v>-13.846153846153</v>
       </c>
       <c r="M19" s="15">
-        <v>-17.054263565891</v>
+        <v>-17.343173431734</v>
       </c>
       <c r="N19" s="15">
-        <v>-55.509355509355</v>
+        <v>-56.164383561643</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" s="15">
-        <v>-57.142857142857</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-50</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>-60</v>
+        <v>-56.25</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.491228070175</v>
+        <v>-96.089385474860</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>44</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="F21" s="17">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G21" s="17">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.285714285714</v>
+        <v>-18.75</v>
       </c>
       <c r="I21" s="17">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="J21" s="17">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.750551876379</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.523809523809</v>
+        <v>-15.178571428571</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.126338329764</v>
+        <v>-22.920892494929</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.302075876879</v>
+        <v>-74.306964164976</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
         <v>9</v>
       </c>
       <c r="H23" s="15">
+        <v>-44.444444444444</v>
+      </c>
+      <c r="I23" s="14">
+        <v>41</v>
+      </c>
+      <c r="J23" s="14">
+        <v>48</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-14.583333333333</v>
+      </c>
+      <c r="L23" s="15">
+        <v>70.833333333333</v>
+      </c>
+      <c r="M23" s="15">
         <v>0</v>
-      </c>
-      <c r="I23" s="14">
-        <v>40</v>
-      </c>
-      <c r="J23" s="14">
-        <v>46</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-13.043478260869</v>
-      </c>
-      <c r="L23" s="15">
-        <v>73.913043478260</v>
-      </c>
-      <c r="M23" s="15">
-        <v>11.111111111111</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D24" s="14">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>-36.585365853658</v>
+        <v>16</v>
       </c>
       <c r="F24" s="14">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G24" s="14">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="H24" s="15">
-        <v>-25.609756097561</v>
+        <v>-6.015037593984</v>
       </c>
       <c r="I24" s="14">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="J24" s="14">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="K24" s="15">
-        <v>-12.569316081330</v>
+        <v>-11.660777385159</v>
       </c>
       <c r="L24" s="15">
-        <v>0.852878464818</v>
+        <v>-0.793650793650</v>
       </c>
       <c r="M24" s="15">
-        <v>-7.797270955165</v>
+        <v>-8.592321755027</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>-21.739130434782</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F25" s="14">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G25" s="14">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="H25" s="15">
-        <v>-10.958904109589</v>
+        <v>23.214285714285</v>
       </c>
       <c r="I25" s="14">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="J25" s="14">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.367041198501</v>
+        <v>-5.797101449275</v>
       </c>
       <c r="L25" s="15">
-        <v>-5.660377358490</v>
+        <v>-9.722222222222</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F26" s="14">
         <v>32</v>
       </c>
       <c r="G26" s="14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H26" s="15">
-        <v>-5.882352941176</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I26" s="14">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J26" s="14">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="K26" s="15">
-        <v>13.636363636363</v>
+        <v>14.705882352941</v>
       </c>
       <c r="L26" s="15">
-        <v>26.050420168067</v>
+        <v>15.555555555555</v>
       </c>
       <c r="M26" s="15">
-        <v>0.671140939597</v>
+        <v>0.645161290322</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,28 +1388,28 @@
         <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
         <v>-100</v>
       </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L27" s="15">
         <v>-55.555555555555</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
+        <v>18</v>
+      </c>
+      <c r="J28" s="14">
         <v>16</v>
       </c>
-      <c r="J28" s="14">
-        <v>14</v>
-      </c>
       <c r="K28" s="15">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.615384615384</v>
+        <v>-76.923076923076</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.888888888888</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="31" spans="1:14">
